--- a/youzi/交易者单骑/index.xlsx
+++ b/youzi/交易者单骑/index.xlsx
@@ -45,84 +45,108 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE4E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB72432"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC1E6CA"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE4E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -135,7 +159,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,19 +171,415 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C584"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,163 +615,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C584"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -363,319 +687,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -687,43 +717,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2234,7 +2234,7 @@
       <c r="C2" t="str">
         <v>600192</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="9" t="str">
         <v>净买: 618.00万</v>
       </c>
       <c r="E2">
@@ -2249,40 +2249,40 @@
       <c r="H2">
         <v>5.03</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="5">
         <v>4.79</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="1">
         <v>15.28</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="10">
         <v>12.18</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="2">
         <v>20.47</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="6">
         <v>8.42</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="11">
         <v>2.46</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="7">
         <v>0.78</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="12">
         <v>-1.42</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="13">
         <v>-0.52</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="3">
         <v>1.17</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="4">
         <v>0.65</v>
       </c>
-      <c r="T2" s="13">
+      <c r="T2" s="8">
         <v>8.29</v>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       <c r="C3" t="str">
         <v>600715</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="18" t="str">
         <v>净买: 1669.10万</v>
       </c>
       <c r="E3">
@@ -2311,40 +2311,40 @@
       <c r="H3">
         <v>0.38</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="25">
         <v>9.74</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="14">
         <v>10.11</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="19">
         <v>20.97</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="20">
         <v>8.99</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="15">
         <v>0.75</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="22">
         <v>1.12</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="23">
         <v>11.24</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="24">
         <v>13.48</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="16">
         <v>13.11</v>
       </c>
       <c r="R3" s="21">
         <v>16.85</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="17">
         <v>14.98</v>
       </c>
-      <c r="T3" s="22">
+      <c r="T3" s="26">
         <v>-24.34</v>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       <c r="C4" t="str">
         <v>301231</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="31" t="str">
         <v>净卖: -1178.30万</v>
       </c>
       <c r="E4">
@@ -2373,40 +2373,40 @@
       <c r="H4">
         <v>6.44</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="36">
         <v>-2.7</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="37">
         <v>16.76</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="27">
         <v>16.15</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="32">
         <v>10.53</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="28">
         <v>9.95</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="34">
         <v>5.4</v>
       </c>
       <c r="O4" s="38">
         <v>1.32</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="33">
         <v>21.58</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="35">
         <v>23.43</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="39">
         <v>21.71</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="29">
         <v>17.16</v>
       </c>
-      <c r="T4" s="37">
+      <c r="T4" s="30">
         <v>-3.29</v>
       </c>
     </row>
@@ -2435,37 +2435,37 @@
       <c r="H5">
         <v>-8.25</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="45">
         <v>-1.97</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="51">
         <v>-5.48</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="47">
         <v>-5.76</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="48">
         <v>-5.06</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="49">
         <v>-6.32</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="46">
         <v>-2.53</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="42">
         <v>1.4</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="52">
         <v>1.83</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="50">
         <v>3.09</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="43">
         <v>3.23</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="44">
         <v>4.63</v>
       </c>
       <c r="T5" s="40">
@@ -2482,7 +2482,7 @@
       <c r="C6" t="str">
         <v>603378</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="61" t="str">
         <v>净卖: -283.77万</v>
       </c>
       <c r="E6">
@@ -2497,40 +2497,40 @@
       <c r="H6">
         <v>-8.77</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="62">
         <v>-1.34</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="55">
         <v>-0.85</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="64">
         <v>0.12</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="63">
         <v>-1.46</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="65">
         <v>-11.31</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="53">
         <v>-10.58</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="56">
         <v>-11.92</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="57">
         <v>-14.6</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="58">
         <v>-11.92</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="54">
         <v>-12.04</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="59">
         <v>-7.3</v>
       </c>
-      <c r="T6" s="63">
+      <c r="T6" s="60">
         <v>-33.09</v>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       <c r="C7" t="str">
         <v>001317</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="69" t="str">
         <v>净买: 1947.09万</v>
       </c>
       <c r="E7">
@@ -2559,19 +2559,19 @@
       <c r="H7">
         <v>2.35</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="77">
         <v>7.48</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="70">
         <v>0.53</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="73">
         <v>5.64</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="78">
         <v>9.11</v>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="71">
         <v>3.83</v>
       </c>
       <c r="N7" s="67">
@@ -2580,19 +2580,19 @@
       <c r="O7" s="74">
         <v>-1.45</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="66">
         <v>0.73</v>
       </c>
       <c r="Q7" s="75">
         <v>2.93</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="68">
         <v>5.28</v>
       </c>
-      <c r="S7" s="70">
+      <c r="S7" s="76">
         <v>3.55</v>
       </c>
-      <c r="T7" s="77">
+      <c r="T7" s="72">
         <v>-6.18</v>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       <c r="C8" t="str">
         <v>603608</v>
       </c>
-      <c r="D8" s="90" t="str">
+      <c r="D8" s="89" t="str">
         <v>净买: 1843.41万</v>
       </c>
       <c r="E8">
@@ -2621,40 +2621,40 @@
       <c r="H8">
         <v>0.09</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="83">
         <v>9.95</v>
       </c>
-      <c r="J8" s="91">
+      <c r="J8" s="81">
         <v>9.12</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="84">
         <v>6.39</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="90">
         <v>3.1</v>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="85">
         <v>1.73</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8" s="80">
         <v>0.27</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="91">
         <v>-0.73</v>
       </c>
-      <c r="P8" s="85">
+      <c r="P8" s="86">
         <v>-4.93</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="79">
         <v>-2.46</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="87">
         <v>-5.47</v>
       </c>
-      <c r="S8" s="86">
+      <c r="S8" s="88">
         <v>-5.47</v>
       </c>
-      <c r="T8" s="89">
+      <c r="T8" s="82">
         <v>5.66</v>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="101">
+      <c r="I10" s="98">
         <v>57.14</v>
       </c>
       <c r="J10" s="93">
@@ -2729,25 +2729,25 @@
       <c r="L10" s="95">
         <v>71.43</v>
       </c>
-      <c r="M10" s="102">
+      <c r="M10" s="96">
         <v>71.43</v>
       </c>
-      <c r="N10" s="96">
+      <c r="N10" s="99">
         <v>71.43</v>
       </c>
-      <c r="O10" s="97">
+      <c r="O10" s="100">
         <v>57.14</v>
       </c>
-      <c r="P10" s="103">
+      <c r="P10" s="97">
         <v>57.14</v>
       </c>
-      <c r="Q10" s="98">
+      <c r="Q10" s="101">
         <v>57.14</v>
       </c>
-      <c r="R10" s="99">
+      <c r="R10" s="103">
         <v>71.43</v>
       </c>
-      <c r="S10" s="100">
+      <c r="S10" s="102">
         <v>71.43</v>
       </c>
       <c r="T10" s="92">
@@ -2765,40 +2765,40 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="110">
+      <c r="I11" s="104">
         <v>3.71</v>
       </c>
-      <c r="J11" s="114">
+      <c r="J11" s="110">
         <v>6.5</v>
       </c>
-      <c r="K11" s="104">
+      <c r="K11" s="111">
         <v>7.96</v>
       </c>
-      <c r="L11" s="107">
+      <c r="L11" s="105">
         <v>6.53</v>
       </c>
-      <c r="M11" s="108">
+      <c r="M11" s="113">
         <v>1.01</v>
       </c>
-      <c r="N11" s="111">
+      <c r="N11" s="112">
         <v>-0.51</v>
       </c>
-      <c r="O11" s="115">
+      <c r="O11" s="114">
         <v>0.09</v>
       </c>
       <c r="P11" s="109">
         <v>2.38</v>
       </c>
-      <c r="Q11" s="105">
+      <c r="Q11" s="106">
         <v>3.95</v>
       </c>
-      <c r="R11" s="106">
+      <c r="R11" s="107">
         <v>4.39</v>
       </c>
-      <c r="S11" s="112">
+      <c r="S11" s="115">
         <v>4.03</v>
       </c>
-      <c r="T11" s="113">
+      <c r="T11" s="108">
         <v>-8.33</v>
       </c>
     </row>

--- a/youzi/交易者单骑/index.xlsx
+++ b/youzi/交易者单骑/index.xlsx
@@ -39,13 +39,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFAE4E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,31 +117,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAE4E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,49 +165,307 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C584"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,43 +477,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,535 +645,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C584"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2234,7 +2234,7 @@
       <c r="C2" t="str">
         <v>600192</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="4" t="str">
         <v>净买: 618.00万</v>
       </c>
       <c r="E2">
@@ -2252,37 +2252,37 @@
       <c r="I2" s="5">
         <v>4.79</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="6">
         <v>15.28</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="7">
         <v>12.18</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="8">
         <v>20.47</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="2">
         <v>8.42</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="9">
         <v>2.46</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="10">
         <v>0.78</v>
       </c>
       <c r="P2" s="12">
         <v>-1.42</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="11">
         <v>-0.52</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="13">
         <v>1.17</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="1">
         <v>0.65</v>
       </c>
-      <c r="T2" s="8">
+      <c r="T2" s="3">
         <v>8.29</v>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       <c r="C3" t="str">
         <v>600715</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="21" t="str">
         <v>净买: 1669.10万</v>
       </c>
       <c r="E3">
@@ -2311,40 +2311,40 @@
       <c r="H3">
         <v>0.38</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="22">
         <v>9.74</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="23">
         <v>10.11</v>
       </c>
       <c r="K3" s="19">
         <v>20.97</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="24">
         <v>8.99</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="14">
         <v>0.75</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="25">
         <v>1.12</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="26">
         <v>11.24</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="20">
         <v>13.48</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="15">
         <v>13.11</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="16">
         <v>16.85</v>
       </c>
       <c r="S3" s="17">
         <v>14.98</v>
       </c>
-      <c r="T3" s="26">
+      <c r="T3" s="18">
         <v>-24.34</v>
       </c>
     </row>
@@ -2373,19 +2373,19 @@
       <c r="H4">
         <v>6.44</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="32">
         <v>-2.7</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="36">
         <v>16.76</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="33">
         <v>16.15</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="28">
         <v>10.53</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="37">
         <v>9.95</v>
       </c>
       <c r="N4" s="34">
@@ -2394,19 +2394,19 @@
       <c r="O4" s="38">
         <v>1.32</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="39">
         <v>21.58</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="29">
         <v>23.43</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="27">
         <v>21.71</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="30">
         <v>17.16</v>
       </c>
-      <c r="T4" s="30">
+      <c r="T4" s="35">
         <v>-3.29</v>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       <c r="C5" t="str">
         <v>000952</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="45" t="str">
         <v>净卖: -615.36万</v>
       </c>
       <c r="E5">
@@ -2435,40 +2435,40 @@
       <c r="H5">
         <v>-8.25</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="46">
         <v>-1.97</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="40">
         <v>-5.48</v>
       </c>
       <c r="K5" s="47">
         <v>-5.76</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="44">
         <v>-5.06</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="50">
         <v>-6.32</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="48">
         <v>-2.53</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="51">
         <v>1.4</v>
       </c>
       <c r="P5" s="52">
         <v>1.83</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="49">
         <v>3.09</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="41">
         <v>3.23</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="42">
         <v>4.63</v>
       </c>
-      <c r="T5" s="40">
+      <c r="T5" s="43">
         <v>-5.34</v>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       <c r="C6" t="str">
         <v>603378</v>
       </c>
-      <c r="D6" s="61" t="str">
+      <c r="D6" s="64" t="str">
         <v>净卖: -283.77万</v>
       </c>
       <c r="E6">
@@ -2497,22 +2497,22 @@
       <c r="H6">
         <v>-8.77</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="65">
         <v>-1.34</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="63">
         <v>-0.85</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="53">
         <v>0.12</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="62">
         <v>-1.46</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="54">
         <v>-11.31</v>
       </c>
-      <c r="N6" s="53">
+      <c r="N6" s="55">
         <v>-10.58</v>
       </c>
       <c r="O6" s="56">
@@ -2521,16 +2521,16 @@
       <c r="P6" s="57">
         <v>-14.6</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="59">
         <v>-11.92</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="58">
         <v>-12.04</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="60">
         <v>-7.3</v>
       </c>
-      <c r="T6" s="60">
+      <c r="T6" s="61">
         <v>-33.09</v>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       <c r="C7" t="str">
         <v>001317</v>
       </c>
-      <c r="D7" s="69" t="str">
+      <c r="D7" s="73" t="str">
         <v>净买: 1947.09万</v>
       </c>
       <c r="E7">
@@ -2559,40 +2559,40 @@
       <c r="H7">
         <v>2.35</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="66">
         <v>7.48</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="74">
         <v>0.53</v>
       </c>
-      <c r="K7" s="73">
+      <c r="K7" s="67">
         <v>5.64</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="68">
         <v>9.11</v>
       </c>
       <c r="M7" s="71">
         <v>3.83</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="75">
         <v>0.26</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="69">
         <v>-1.45</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="76">
         <v>0.73</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="77">
         <v>2.93</v>
       </c>
-      <c r="R7" s="68">
+      <c r="R7" s="78">
         <v>5.28</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="72">
         <v>3.55</v>
       </c>
-      <c r="T7" s="72">
+      <c r="T7" s="70">
         <v>-6.18</v>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       <c r="C8" t="str">
         <v>603608</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="83" t="str">
         <v>净买: 1843.41万</v>
       </c>
       <c r="E8">
@@ -2621,40 +2621,40 @@
       <c r="H8">
         <v>0.09</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="80">
         <v>9.95</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="84">
         <v>9.12</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="87">
         <v>6.39</v>
       </c>
-      <c r="L8" s="90">
+      <c r="L8" s="85">
         <v>3.1</v>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="88">
         <v>1.73</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="90">
         <v>0.27</v>
       </c>
-      <c r="O8" s="91">
+      <c r="O8" s="89">
         <v>-0.73</v>
       </c>
       <c r="P8" s="86">
         <v>-4.93</v>
       </c>
-      <c r="Q8" s="79">
+      <c r="Q8" s="81">
         <v>-2.46</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="91">
         <v>-5.47</v>
       </c>
-      <c r="S8" s="88">
+      <c r="S8" s="82">
         <v>-5.47</v>
       </c>
-      <c r="T8" s="82">
+      <c r="T8" s="79">
         <v>5.66</v>
       </c>
     </row>
@@ -2717,40 +2717,40 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="98">
+      <c r="I10" s="102">
         <v>57.14</v>
       </c>
-      <c r="J10" s="93">
+      <c r="J10" s="103">
         <v>71.43</v>
       </c>
-      <c r="K10" s="94">
+      <c r="K10" s="92">
         <v>85.71</v>
       </c>
-      <c r="L10" s="95">
+      <c r="L10" s="99">
         <v>71.43</v>
       </c>
-      <c r="M10" s="96">
+      <c r="M10" s="93">
         <v>71.43</v>
       </c>
-      <c r="N10" s="99">
+      <c r="N10" s="97">
         <v>71.43</v>
       </c>
       <c r="O10" s="100">
         <v>57.14</v>
       </c>
-      <c r="P10" s="97">
+      <c r="P10" s="95">
         <v>57.14</v>
       </c>
-      <c r="Q10" s="101">
+      <c r="Q10" s="94">
         <v>57.14</v>
       </c>
-      <c r="R10" s="103">
+      <c r="R10" s="96">
         <v>71.43</v>
       </c>
-      <c r="S10" s="102">
+      <c r="S10" s="98">
         <v>71.43</v>
       </c>
-      <c r="T10" s="92">
+      <c r="T10" s="101">
         <v>28.57</v>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="104">
+      <c r="I11" s="113">
         <v>3.71</v>
       </c>
       <c r="J11" s="110">
@@ -2774,31 +2774,31 @@
       <c r="K11" s="111">
         <v>7.96</v>
       </c>
-      <c r="L11" s="105">
+      <c r="L11" s="104">
         <v>6.53</v>
       </c>
-      <c r="M11" s="113">
+      <c r="M11" s="106">
         <v>1.01</v>
       </c>
-      <c r="N11" s="112">
+      <c r="N11" s="114">
         <v>-0.51</v>
       </c>
-      <c r="O11" s="114">
+      <c r="O11" s="107">
         <v>0.09</v>
       </c>
-      <c r="P11" s="109">
+      <c r="P11" s="108">
         <v>2.38</v>
       </c>
-      <c r="Q11" s="106">
+      <c r="Q11" s="109">
         <v>3.95</v>
       </c>
-      <c r="R11" s="107">
+      <c r="R11" s="112">
         <v>4.39</v>
       </c>
-      <c r="S11" s="115">
+      <c r="S11" s="105">
         <v>4.03</v>
       </c>
-      <c r="T11" s="108">
+      <c r="T11" s="115">
         <v>-8.33</v>
       </c>
     </row>

--- a/youzi/交易者单骑/index.xlsx
+++ b/youzi/交易者单骑/index.xlsx
@@ -39,19 +39,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFAE4E6"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,55 +111,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,66 +165,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF7D1D5"/>
         <bgColor/>
       </patternFill>
@@ -219,12 +213,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF8ACF9A"/>
         <bgColor/>
       </patternFill>
@@ -237,48 +273,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C584"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF26A142"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE87C86"/>
         <bgColor/>
       </patternFill>
@@ -291,7 +303,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -303,6 +321,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -315,37 +351,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -357,12 +369,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -381,205 +411,229 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -603,61 +657,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -675,18 +711,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA81D2A"/>
         <bgColor/>
       </patternFill>
@@ -694,30 +718,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2234,7 +2234,7 @@
       <c r="C2" t="str">
         <v>600192</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="12" t="str">
         <v>净买: 618.00万</v>
       </c>
       <c r="E2">
@@ -2249,41 +2249,41 @@
       <c r="H2">
         <v>5.03</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="9">
         <v>4.79</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="13">
         <v>15.28</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="10">
         <v>12.18</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="1">
         <v>20.47</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="4">
         <v>8.42</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="11">
         <v>2.46</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="6">
         <v>0.78</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="2">
         <v>-1.42</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="7">
         <v>-0.52</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="3">
         <v>1.17</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="8">
         <v>0.65</v>
       </c>
-      <c r="T2" s="3">
-        <v>8.29</v>
+      <c r="T2" s="5">
+        <v>9.46</v>
       </c>
     </row>
     <row r="3">
@@ -2296,7 +2296,7 @@
       <c r="C3" t="str">
         <v>600715</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="23" t="str">
         <v>净买: 1669.10万</v>
       </c>
       <c r="E3">
@@ -2311,40 +2311,40 @@
       <c r="H3">
         <v>0.38</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="19">
         <v>9.74</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="14">
         <v>10.11</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="15">
         <v>20.97</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="20">
         <v>8.99</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="21">
         <v>0.75</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="24">
         <v>1.12</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="25">
         <v>11.24</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="26">
         <v>13.48</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="16">
         <v>13.11</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="17">
         <v>16.85</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="18">
         <v>14.98</v>
       </c>
-      <c r="T3" s="18">
+      <c r="T3" s="22">
         <v>-24.34</v>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       <c r="C4" t="str">
         <v>301231</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="35" t="str">
         <v>净卖: -1178.30万</v>
       </c>
       <c r="E4">
@@ -2373,41 +2373,41 @@
       <c r="H4">
         <v>6.44</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="38">
         <v>-2.7</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="39">
         <v>16.76</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="27">
         <v>16.15</v>
       </c>
       <c r="L4" s="28">
         <v>10.53</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="29">
         <v>9.95</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="30">
         <v>5.4</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="36">
         <v>1.32</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="31">
         <v>21.58</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="37">
         <v>23.43</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="32">
         <v>21.71</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="33">
         <v>17.16</v>
       </c>
-      <c r="T4" s="35">
-        <v>-3.29</v>
+      <c r="T4" s="34">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="5">
@@ -2420,7 +2420,7 @@
       <c r="C5" t="str">
         <v>000952</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="51" t="str">
         <v>净卖: -615.36万</v>
       </c>
       <c r="E5">
@@ -2435,41 +2435,41 @@
       <c r="H5">
         <v>-8.25</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="52">
         <v>-1.97</v>
       </c>
       <c r="J5" s="40">
         <v>-5.48</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="41">
         <v>-5.76</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="47">
         <v>-5.06</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="42">
         <v>-6.32</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="45">
         <v>-2.53</v>
       </c>
-      <c r="O5" s="51">
+      <c r="O5" s="49">
         <v>1.4</v>
       </c>
-      <c r="P5" s="52">
+      <c r="P5" s="46">
         <v>1.83</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="48">
         <v>3.09</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="43">
         <v>3.23</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="44">
         <v>4.63</v>
       </c>
-      <c r="T5" s="43">
-        <v>-5.34</v>
+      <c r="T5" s="50">
+        <v>-5.62</v>
       </c>
     </row>
     <row r="6">
@@ -2482,7 +2482,7 @@
       <c r="C6" t="str">
         <v>603378</v>
       </c>
-      <c r="D6" s="64" t="str">
+      <c r="D6" s="63" t="str">
         <v>净卖: -283.77万</v>
       </c>
       <c r="E6">
@@ -2497,41 +2497,41 @@
       <c r="H6">
         <v>-8.77</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="64">
         <v>-1.34</v>
       </c>
-      <c r="J6" s="63">
+      <c r="J6" s="57">
         <v>-0.85</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="55">
         <v>0.12</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="59">
         <v>-1.46</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="60">
         <v>-11.31</v>
       </c>
-      <c r="N6" s="55">
+      <c r="N6" s="61">
         <v>-10.58</v>
       </c>
-      <c r="O6" s="56">
+      <c r="O6" s="65">
         <v>-11.92</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="58">
         <v>-14.6</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="53">
         <v>-11.92</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="62">
         <v>-12.04</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="56">
         <v>-7.3</v>
       </c>
-      <c r="T6" s="61">
-        <v>-33.09</v>
+      <c r="T6" s="54">
+        <v>-32.36</v>
       </c>
     </row>
     <row r="7">
@@ -2544,7 +2544,7 @@
       <c r="C7" t="str">
         <v>001317</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="66" t="str">
         <v>净买: 1947.09万</v>
       </c>
       <c r="E7">
@@ -2559,41 +2559,41 @@
       <c r="H7">
         <v>2.35</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="72">
         <v>7.48</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="71">
         <v>0.53</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="73">
         <v>5.64</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="67">
         <v>9.11</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="68">
         <v>3.83</v>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="69">
         <v>0.26</v>
       </c>
-      <c r="O7" s="69">
+      <c r="O7" s="76">
         <v>-1.45</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="77">
         <v>0.73</v>
       </c>
-      <c r="Q7" s="77">
+      <c r="Q7" s="74">
         <v>2.93</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="75">
         <v>5.28</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="70">
         <v>3.55</v>
       </c>
-      <c r="T7" s="70">
-        <v>-6.18</v>
+      <c r="T7" s="78">
+        <v>-4.62</v>
       </c>
     </row>
     <row r="8">
@@ -2606,7 +2606,7 @@
       <c r="C8" t="str">
         <v>603608</v>
       </c>
-      <c r="D8" s="83" t="str">
+      <c r="D8" s="87" t="str">
         <v>净买: 1843.41万</v>
       </c>
       <c r="E8">
@@ -2621,41 +2621,41 @@
       <c r="H8">
         <v>0.09</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="83">
         <v>9.95</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="88">
         <v>9.12</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="89">
         <v>6.39</v>
       </c>
-      <c r="L8" s="85">
+      <c r="L8" s="90">
         <v>3.1</v>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="79">
         <v>1.73</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="80">
         <v>0.27</v>
       </c>
-      <c r="O8" s="89">
+      <c r="O8" s="84">
         <v>-0.73</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="85">
         <v>-4.93</v>
       </c>
-      <c r="Q8" s="81">
+      <c r="Q8" s="86">
         <v>-2.46</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="81">
         <v>-5.47</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="91">
         <v>-5.47</v>
       </c>
-      <c r="T8" s="79">
-        <v>5.66</v>
+      <c r="T8" s="82">
+        <v>10.95</v>
       </c>
     </row>
     <row r="9">
@@ -2717,40 +2717,40 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="102">
+      <c r="I10" s="92">
         <v>57.14</v>
       </c>
-      <c r="J10" s="103">
+      <c r="J10" s="102">
         <v>71.43</v>
       </c>
-      <c r="K10" s="92">
+      <c r="K10" s="93">
         <v>85.71</v>
       </c>
       <c r="L10" s="99">
         <v>71.43</v>
       </c>
-      <c r="M10" s="93">
+      <c r="M10" s="100">
         <v>71.43</v>
       </c>
-      <c r="N10" s="97">
+      <c r="N10" s="94">
         <v>71.43</v>
       </c>
-      <c r="O10" s="100">
+      <c r="O10" s="95">
         <v>57.14</v>
       </c>
-      <c r="P10" s="95">
+      <c r="P10" s="96">
         <v>57.14</v>
       </c>
-      <c r="Q10" s="94">
+      <c r="Q10" s="103">
         <v>57.14</v>
       </c>
-      <c r="R10" s="96">
+      <c r="R10" s="101">
         <v>71.43</v>
       </c>
-      <c r="S10" s="98">
+      <c r="S10" s="97">
         <v>71.43</v>
       </c>
-      <c r="T10" s="101">
+      <c r="T10" s="98">
         <v>28.57</v>
       </c>
     </row>
@@ -2765,41 +2765,41 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="113">
+      <c r="I11" s="106">
         <v>3.71</v>
       </c>
-      <c r="J11" s="110">
+      <c r="J11" s="107">
         <v>6.5</v>
       </c>
-      <c r="K11" s="111">
+      <c r="K11" s="108">
         <v>7.96</v>
       </c>
       <c r="L11" s="104">
         <v>6.53</v>
       </c>
-      <c r="M11" s="106">
+      <c r="M11" s="112">
         <v>1.01</v>
       </c>
-      <c r="N11" s="114">
+      <c r="N11" s="109">
         <v>-0.51</v>
       </c>
-      <c r="O11" s="107">
+      <c r="O11" s="110">
         <v>0.09</v>
       </c>
-      <c r="P11" s="108">
+      <c r="P11" s="105">
         <v>2.38</v>
       </c>
-      <c r="Q11" s="109">
+      <c r="Q11" s="113">
         <v>3.95</v>
       </c>
-      <c r="R11" s="112">
+      <c r="R11" s="111">
         <v>4.39</v>
       </c>
-      <c r="S11" s="105">
+      <c r="S11" s="114">
         <v>4.03</v>
       </c>
       <c r="T11" s="115">
-        <v>-8.33</v>
+        <v>-6.73</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/交易者单骑/index.xlsx
+++ b/youzi/交易者单骑/index.xlsx
@@ -39,7 +39,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -51,19 +63,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF6CFD3"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
+        <fgColor rgb="FFFAE4E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,18 +93,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE4E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDD3D4C"/>
         <bgColor/>
       </patternFill>
@@ -99,7 +105,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,19 +165,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF7D1D5"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,7 +195,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,103 +381,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,73 +525,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB5"/>
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -357,306 +645,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -669,61 +717,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A1"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2234,7 +2234,7 @@
       <c r="C2" t="str">
         <v>600192</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="2" t="str">
         <v>净买: 618.00万</v>
       </c>
       <c r="E2">
@@ -2249,41 +2249,41 @@
       <c r="H2">
         <v>5.03</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>4.79</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="11">
         <v>15.28</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="12">
         <v>12.18</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="13">
         <v>20.47</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="3">
         <v>8.42</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="1">
         <v>2.46</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="9">
         <v>0.78</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="4">
         <v>-1.42</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="5">
         <v>-0.52</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="6">
         <v>1.17</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="7">
         <v>0.65</v>
       </c>
-      <c r="T2" s="5">
-        <v>9.46</v>
+      <c r="T2" s="8">
+        <v>7.77</v>
       </c>
     </row>
     <row r="3">
@@ -2296,7 +2296,7 @@
       <c r="C3" t="str">
         <v>600715</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="20" t="str">
         <v>净买: 1669.10万</v>
       </c>
       <c r="E3">
@@ -2311,31 +2311,31 @@
       <c r="H3">
         <v>0.38</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="25">
         <v>9.74</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="21">
         <v>10.11</v>
       </c>
       <c r="K3" s="15">
         <v>20.97</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="26">
         <v>8.99</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="14">
         <v>0.75</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="22">
         <v>1.12</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="16">
         <v>11.24</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="23">
         <v>13.48</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="24">
         <v>13.11</v>
       </c>
       <c r="R3" s="17">
@@ -2344,8 +2344,8 @@
       <c r="S3" s="18">
         <v>14.98</v>
       </c>
-      <c r="T3" s="22">
-        <v>-24.34</v>
+      <c r="T3" s="19">
+        <v>-16.85</v>
       </c>
     </row>
     <row r="4">
@@ -2358,7 +2358,7 @@
       <c r="C4" t="str">
         <v>301231</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="27" t="str">
         <v>净卖: -1178.30万</v>
       </c>
       <c r="E4">
@@ -2373,41 +2373,41 @@
       <c r="H4">
         <v>6.44</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="30">
         <v>-2.7</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="38">
         <v>16.76</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="33">
         <v>16.15</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="34">
         <v>10.53</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="35">
         <v>9.95</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="39">
         <v>5.4</v>
       </c>
       <c r="O4" s="36">
         <v>1.32</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="28">
         <v>21.58</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="29">
         <v>23.43</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="37">
         <v>21.71</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="31">
         <v>17.16</v>
       </c>
-      <c r="T4" s="34">
-        <v>-0.58</v>
+      <c r="T4" s="32">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="5">
@@ -2420,7 +2420,7 @@
       <c r="C5" t="str">
         <v>000952</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="40" t="str">
         <v>净卖: -615.36万</v>
       </c>
       <c r="E5">
@@ -2435,41 +2435,41 @@
       <c r="H5">
         <v>-8.25</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="51">
         <v>-1.97</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="41">
         <v>-5.48</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="48">
         <v>-5.76</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="49">
         <v>-5.06</v>
       </c>
       <c r="M5" s="42">
         <v>-6.32</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="46">
         <v>-2.53</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="43">
         <v>1.4</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="44">
         <v>1.83</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="45">
         <v>3.09</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="52">
         <v>3.23</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="47">
         <v>4.63</v>
       </c>
       <c r="T5" s="50">
-        <v>-5.62</v>
+        <v>-6.32</v>
       </c>
     </row>
     <row r="6">
@@ -2482,7 +2482,7 @@
       <c r="C6" t="str">
         <v>603378</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="58" t="str">
         <v>净卖: -283.77万</v>
       </c>
       <c r="E6">
@@ -2497,41 +2497,41 @@
       <c r="H6">
         <v>-8.77</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="54">
         <v>-1.34</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="55">
         <v>-0.85</v>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="56">
         <v>0.12</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="61">
         <v>-1.46</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="62">
         <v>-11.31</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="64">
         <v>-10.58</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="63">
         <v>-11.92</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="59">
         <v>-14.6</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="65">
         <v>-11.92</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="57">
         <v>-12.04</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="53">
         <v>-7.3</v>
       </c>
-      <c r="T6" s="54">
-        <v>-32.36</v>
+      <c r="T6" s="60">
+        <v>-32.24</v>
       </c>
     </row>
     <row r="7">
@@ -2559,41 +2559,41 @@
       <c r="H7">
         <v>2.35</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="77">
         <v>7.48</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="74">
         <v>0.53</v>
       </c>
-      <c r="K7" s="73">
+      <c r="K7" s="75">
         <v>5.64</v>
       </c>
       <c r="L7" s="67">
         <v>9.11</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="72">
         <v>3.83</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="68">
         <v>0.26</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="78">
         <v>-1.45</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="69">
         <v>0.73</v>
       </c>
-      <c r="Q7" s="74">
+      <c r="Q7" s="76">
         <v>2.93</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="70">
         <v>5.28</v>
       </c>
-      <c r="S7" s="70">
+      <c r="S7" s="73">
         <v>3.55</v>
       </c>
-      <c r="T7" s="78">
-        <v>-4.62</v>
+      <c r="T7" s="71">
+        <v>-5.67</v>
       </c>
     </row>
     <row r="8">
@@ -2621,28 +2621,28 @@
       <c r="H8">
         <v>0.09</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="88">
         <v>9.95</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="82">
         <v>9.12</v>
       </c>
-      <c r="K8" s="89">
+      <c r="K8" s="91">
         <v>6.39</v>
       </c>
-      <c r="L8" s="90">
+      <c r="L8" s="83">
         <v>3.1</v>
       </c>
-      <c r="M8" s="79">
+      <c r="M8" s="84">
         <v>1.73</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="79">
         <v>0.27</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="85">
         <v>-0.73</v>
       </c>
-      <c r="P8" s="85">
+      <c r="P8" s="80">
         <v>-4.93</v>
       </c>
       <c r="Q8" s="86">
@@ -2651,11 +2651,11 @@
       <c r="R8" s="81">
         <v>-5.47</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="89">
         <v>-5.47</v>
       </c>
-      <c r="T8" s="82">
-        <v>10.95</v>
+      <c r="T8" s="90">
+        <v>18.07</v>
       </c>
     </row>
     <row r="9">
@@ -2717,40 +2717,40 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="92">
+      <c r="I10" s="102">
         <v>57.14</v>
       </c>
-      <c r="J10" s="102">
+      <c r="J10" s="94">
         <v>71.43</v>
       </c>
-      <c r="K10" s="93">
+      <c r="K10" s="99">
         <v>85.71</v>
       </c>
-      <c r="L10" s="99">
+      <c r="L10" s="103">
         <v>71.43</v>
       </c>
-      <c r="M10" s="100">
+      <c r="M10" s="92">
         <v>71.43</v>
       </c>
-      <c r="N10" s="94">
+      <c r="N10" s="95">
         <v>71.43</v>
       </c>
-      <c r="O10" s="95">
+      <c r="O10" s="93">
         <v>57.14</v>
       </c>
-      <c r="P10" s="96">
+      <c r="P10" s="97">
         <v>57.14</v>
       </c>
-      <c r="Q10" s="103">
+      <c r="Q10" s="96">
         <v>57.14</v>
       </c>
-      <c r="R10" s="101">
+      <c r="R10" s="98">
         <v>71.43</v>
       </c>
-      <c r="S10" s="97">
+      <c r="S10" s="100">
         <v>71.43</v>
       </c>
-      <c r="T10" s="98">
+      <c r="T10" s="101">
         <v>28.57</v>
       </c>
     </row>
@@ -2765,41 +2765,41 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="106">
+      <c r="I11" s="108">
         <v>3.71</v>
       </c>
-      <c r="J11" s="107">
+      <c r="J11" s="112">
         <v>6.5</v>
       </c>
-      <c r="K11" s="108">
+      <c r="K11" s="114">
         <v>7.96</v>
       </c>
-      <c r="L11" s="104">
+      <c r="L11" s="105">
         <v>6.53</v>
       </c>
-      <c r="M11" s="112">
+      <c r="M11" s="106">
         <v>1.01</v>
       </c>
       <c r="N11" s="109">
         <v>-0.51</v>
       </c>
-      <c r="O11" s="110">
+      <c r="O11" s="107">
         <v>0.09</v>
       </c>
-      <c r="P11" s="105">
+      <c r="P11" s="113">
         <v>2.38</v>
       </c>
-      <c r="Q11" s="113">
+      <c r="Q11" s="115">
         <v>3.95</v>
       </c>
-      <c r="R11" s="111">
+      <c r="R11" s="104">
         <v>4.39</v>
       </c>
-      <c r="S11" s="114">
+      <c r="S11" s="110">
         <v>4.03</v>
       </c>
-      <c r="T11" s="115">
-        <v>-6.73</v>
+      <c r="T11" s="111">
+        <v>-5.2</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/交易者单骑/index.xlsx
+++ b/youzi/交易者单骑/index.xlsx
@@ -45,6 +45,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE4E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -57,61 +117,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE4E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,25 +189,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,127 +357,199 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,91 +561,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -381,7 +597,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -393,271 +693,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259F41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -675,55 +711,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFDF5F6"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2234,7 +2234,7 @@
       <c r="C2" t="str">
         <v>600192</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="12" t="str">
         <v>净买: 618.00万</v>
       </c>
       <c r="E2">
@@ -2249,41 +2249,41 @@
       <c r="H2">
         <v>5.03</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="8">
         <v>4.79</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="4">
         <v>15.28</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="9">
         <v>12.18</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="10">
         <v>20.47</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="13">
         <v>8.42</v>
       </c>
       <c r="N2" s="1">
         <v>2.46</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="6">
         <v>0.78</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="5">
         <v>-1.42</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="11">
         <v>-0.52</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="2">
         <v>1.17</v>
       </c>
       <c r="S2" s="7">
         <v>0.65</v>
       </c>
-      <c r="T2" s="8">
-        <v>7.77</v>
+      <c r="T2" s="3">
+        <v>5.83</v>
       </c>
     </row>
     <row r="3">
@@ -2296,7 +2296,7 @@
       <c r="C3" t="str">
         <v>600715</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="21" t="str">
         <v>净买: 1669.10万</v>
       </c>
       <c r="E3">
@@ -2311,41 +2311,41 @@
       <c r="H3">
         <v>0.38</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="22">
         <v>9.74</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="17">
         <v>10.11</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="23">
         <v>20.97</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="24">
         <v>8.99</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="25">
         <v>0.75</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="26">
         <v>1.12</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="14">
         <v>11.24</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="18">
         <v>13.48</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="15">
         <v>13.11</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="16">
         <v>16.85</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="20">
         <v>14.98</v>
       </c>
       <c r="T3" s="19">
-        <v>-16.85</v>
+        <v>-23.22</v>
       </c>
     </row>
     <row r="4">
@@ -2358,7 +2358,7 @@
       <c r="C4" t="str">
         <v>301231</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="38" t="str">
         <v>净卖: -1178.30万</v>
       </c>
       <c r="E4">
@@ -2373,41 +2373,41 @@
       <c r="H4">
         <v>6.44</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="33">
         <v>-2.7</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="39">
         <v>16.76</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="32">
         <v>16.15</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="27">
         <v>10.53</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="28">
         <v>9.95</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="35">
         <v>5.4</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="29">
         <v>1.32</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="30">
         <v>21.58</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="36">
         <v>23.43</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="34">
         <v>21.71</v>
       </c>
       <c r="S4" s="31">
         <v>17.16</v>
       </c>
-      <c r="T4" s="32">
-        <v>-1.14</v>
+      <c r="T4" s="37">
+        <v>-5.34</v>
       </c>
     </row>
     <row r="5">
@@ -2420,7 +2420,7 @@
       <c r="C5" t="str">
         <v>000952</v>
       </c>
-      <c r="D5" s="40" t="str">
+      <c r="D5" s="46" t="str">
         <v>净卖: -615.36万</v>
       </c>
       <c r="E5">
@@ -2435,41 +2435,41 @@
       <c r="H5">
         <v>-8.25</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="47">
         <v>-1.97</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="48">
         <v>-5.48</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="43">
         <v>-5.76</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="44">
         <v>-5.06</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="51">
         <v>-6.32</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="49">
         <v>-2.53</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="52">
         <v>1.4</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="50">
         <v>1.83</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="40">
         <v>3.09</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="45">
         <v>3.23</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="42">
         <v>4.63</v>
       </c>
-      <c r="T5" s="50">
-        <v>-6.32</v>
+      <c r="T5" s="41">
+        <v>-6.18</v>
       </c>
     </row>
     <row r="6">
@@ -2482,7 +2482,7 @@
       <c r="C6" t="str">
         <v>603378</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="62" t="str">
         <v>净卖: -283.77万</v>
       </c>
       <c r="E6">
@@ -2497,41 +2497,41 @@
       <c r="H6">
         <v>-8.77</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="63">
         <v>-1.34</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="59">
         <v>-0.85</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="64">
         <v>0.12</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="57">
         <v>-1.46</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="60">
         <v>-11.31</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="53">
         <v>-10.58</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="54">
         <v>-11.92</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="58">
         <v>-14.6</v>
       </c>
       <c r="Q6" s="65">
         <v>-11.92</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="61">
         <v>-12.04</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="55">
         <v>-7.3</v>
       </c>
-      <c r="T6" s="60">
-        <v>-32.24</v>
+      <c r="T6" s="56">
+        <v>-31.75</v>
       </c>
     </row>
     <row r="7">
@@ -2544,7 +2544,7 @@
       <c r="C7" t="str">
         <v>001317</v>
       </c>
-      <c r="D7" s="66" t="str">
+      <c r="D7" s="73" t="str">
         <v>净买: 1947.09万</v>
       </c>
       <c r="E7">
@@ -2559,41 +2559,41 @@
       <c r="H7">
         <v>2.35</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="67">
         <v>7.48</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="70">
         <v>0.53</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="74">
         <v>5.64</v>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="71">
         <v>9.11</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="75">
         <v>3.83</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="78">
         <v>0.26</v>
       </c>
-      <c r="O7" s="78">
+      <c r="O7" s="68">
         <v>-1.45</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="76">
         <v>0.73</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="69">
         <v>2.93</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="72">
         <v>5.28</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="77">
         <v>3.55</v>
       </c>
-      <c r="T7" s="71">
-        <v>-5.67</v>
+      <c r="T7" s="66">
+        <v>-4.34</v>
       </c>
     </row>
     <row r="8">
@@ -2606,7 +2606,7 @@
       <c r="C8" t="str">
         <v>603608</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="80" t="str">
         <v>净买: 1843.41万</v>
       </c>
       <c r="E8">
@@ -2621,41 +2621,41 @@
       <c r="H8">
         <v>0.09</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="81">
         <v>9.95</v>
       </c>
-      <c r="J8" s="82">
+      <c r="J8" s="85">
         <v>9.12</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="88">
         <v>6.39</v>
       </c>
-      <c r="L8" s="83">
+      <c r="L8" s="89">
         <v>3.1</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="82">
         <v>1.73</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="90">
         <v>0.27</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="83">
         <v>-0.73</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="86">
         <v>-4.93</v>
       </c>
-      <c r="Q8" s="86">
+      <c r="Q8" s="84">
         <v>-2.46</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="91">
         <v>-5.47</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="87">
         <v>-5.47</v>
       </c>
-      <c r="T8" s="90">
-        <v>18.07</v>
+      <c r="T8" s="79">
+        <v>16.51</v>
       </c>
     </row>
     <row r="9">
@@ -2717,40 +2717,40 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="102">
+      <c r="I10" s="98">
         <v>57.14</v>
       </c>
       <c r="J10" s="94">
         <v>71.43</v>
       </c>
-      <c r="K10" s="99">
+      <c r="K10" s="103">
         <v>85.71</v>
       </c>
-      <c r="L10" s="103">
+      <c r="L10" s="99">
         <v>71.43</v>
       </c>
-      <c r="M10" s="92">
+      <c r="M10" s="97">
         <v>71.43</v>
       </c>
-      <c r="N10" s="95">
+      <c r="N10" s="100">
         <v>71.43</v>
       </c>
-      <c r="O10" s="93">
+      <c r="O10" s="101">
         <v>57.14</v>
       </c>
-      <c r="P10" s="97">
+      <c r="P10" s="92">
         <v>57.14</v>
       </c>
-      <c r="Q10" s="96">
+      <c r="Q10" s="95">
         <v>57.14</v>
       </c>
-      <c r="R10" s="98">
+      <c r="R10" s="96">
         <v>71.43</v>
       </c>
-      <c r="S10" s="100">
+      <c r="S10" s="102">
         <v>71.43</v>
       </c>
-      <c r="T10" s="101">
+      <c r="T10" s="93">
         <v>28.57</v>
       </c>
     </row>
@@ -2765,41 +2765,41 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="108">
+      <c r="I11" s="110">
         <v>3.71</v>
       </c>
-      <c r="J11" s="112">
+      <c r="J11" s="105">
         <v>6.5</v>
       </c>
-      <c r="K11" s="114">
+      <c r="K11" s="106">
         <v>7.96</v>
       </c>
-      <c r="L11" s="105">
+      <c r="L11" s="111">
         <v>6.53</v>
       </c>
-      <c r="M11" s="106">
+      <c r="M11" s="112">
         <v>1.01</v>
       </c>
-      <c r="N11" s="109">
+      <c r="N11" s="113">
         <v>-0.51</v>
       </c>
-      <c r="O11" s="107">
+      <c r="O11" s="114">
         <v>0.09</v>
       </c>
-      <c r="P11" s="113">
+      <c r="P11" s="115">
         <v>2.38</v>
       </c>
-      <c r="Q11" s="115">
+      <c r="Q11" s="107">
         <v>3.95</v>
       </c>
-      <c r="R11" s="104">
+      <c r="R11" s="108">
         <v>4.39</v>
       </c>
-      <c r="S11" s="110">
+      <c r="S11" s="104">
         <v>4.03</v>
       </c>
-      <c r="T11" s="111">
-        <v>-5.2</v>
+      <c r="T11" s="109">
+        <v>-6.93</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/交易者单骑/index.xlsx
+++ b/youzi/交易者单骑/index.xlsx
@@ -39,67 +39,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE4E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFED9BA3"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE4E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,37 +183,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,7 +357,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,187 +507,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF26A142"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
+        <fgColor rgb="FFDFF2E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -357,337 +669,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -705,25 +717,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFED98A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2234,7 +2234,7 @@
       <c r="C2" t="str">
         <v>600192</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="4" t="str">
         <v>净买: 618.00万</v>
       </c>
       <c r="E2">
@@ -2249,41 +2249,41 @@
       <c r="H2">
         <v>5.03</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="11">
         <v>4.79</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="9">
         <v>15.28</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="12">
         <v>12.18</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="5">
         <v>20.47</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="6">
         <v>8.42</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="13">
         <v>2.46</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="1">
         <v>0.78</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="2">
         <v>-1.42</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="3">
         <v>-0.52</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="7">
         <v>1.17</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="8">
         <v>0.65</v>
       </c>
-      <c r="T2" s="3">
-        <v>5.83</v>
+      <c r="T2" s="10">
+        <v>6.74</v>
       </c>
     </row>
     <row r="3">
@@ -2296,7 +2296,7 @@
       <c r="C3" t="str">
         <v>600715</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="24" t="str">
         <v>净买: 1669.10万</v>
       </c>
       <c r="E3">
@@ -2311,40 +2311,40 @@
       <c r="H3">
         <v>0.38</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="25">
         <v>9.74</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="18">
         <v>10.11</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="15">
         <v>20.97</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="19">
         <v>8.99</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="16">
         <v>0.75</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="17">
         <v>1.12</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="22">
         <v>11.24</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="20">
         <v>13.48</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="23">
         <v>13.11</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="26">
         <v>16.85</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="21">
         <v>14.98</v>
       </c>
-      <c r="T3" s="19">
+      <c r="T3" s="14">
         <v>-23.22</v>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       <c r="C4" t="str">
         <v>301231</v>
       </c>
-      <c r="D4" s="38" t="str">
+      <c r="D4" s="29" t="str">
         <v>净卖: -1178.30万</v>
       </c>
       <c r="E4">
@@ -2373,41 +2373,41 @@
       <c r="H4">
         <v>6.44</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="35">
         <v>-2.7</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="30">
         <v>16.76</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="36">
         <v>16.15</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="31">
         <v>10.53</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="37">
         <v>9.95</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="32">
         <v>5.4</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="38">
         <v>1.32</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="33">
         <v>21.58</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="39">
         <v>23.43</v>
       </c>
       <c r="R4" s="34">
         <v>21.71</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="27">
         <v>17.16</v>
       </c>
-      <c r="T4" s="37">
-        <v>-5.34</v>
+      <c r="T4" s="28">
+        <v>-5.53</v>
       </c>
     </row>
     <row r="5">
@@ -2420,7 +2420,7 @@
       <c r="C5" t="str">
         <v>000952</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="44" t="str">
         <v>净卖: -615.36万</v>
       </c>
       <c r="E5">
@@ -2435,41 +2435,41 @@
       <c r="H5">
         <v>-8.25</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="40">
         <v>-1.97</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="41">
         <v>-5.48</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="51">
         <v>-5.76</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="45">
         <v>-5.06</v>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="46">
         <v>-6.32</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="48">
         <v>-2.53</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="42">
         <v>1.4</v>
       </c>
-      <c r="P5" s="50">
+      <c r="P5" s="49">
         <v>1.83</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="47">
         <v>3.09</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="43">
         <v>3.23</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="52">
         <v>4.63</v>
       </c>
-      <c r="T5" s="41">
-        <v>-6.18</v>
+      <c r="T5" s="50">
+        <v>3.23</v>
       </c>
     </row>
     <row r="6">
@@ -2482,7 +2482,7 @@
       <c r="C6" t="str">
         <v>603378</v>
       </c>
-      <c r="D6" s="62" t="str">
+      <c r="D6" s="56" t="str">
         <v>净卖: -283.77万</v>
       </c>
       <c r="E6">
@@ -2497,41 +2497,41 @@
       <c r="H6">
         <v>-8.77</v>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="64">
         <v>-1.34</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="54">
         <v>-0.85</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="55">
         <v>0.12</v>
       </c>
       <c r="L6" s="57">
         <v>-1.46</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="65">
         <v>-11.31</v>
       </c>
-      <c r="N6" s="53">
+      <c r="N6" s="58">
         <v>-10.58</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="59">
         <v>-11.92</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="60">
         <v>-14.6</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="61">
         <v>-11.92</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="53">
         <v>-12.04</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="62">
         <v>-7.3</v>
       </c>
-      <c r="T6" s="56">
-        <v>-31.75</v>
+      <c r="T6" s="63">
+        <v>-30.29</v>
       </c>
     </row>
     <row r="7">
@@ -2544,7 +2544,7 @@
       <c r="C7" t="str">
         <v>001317</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="78" t="str">
         <v>净买: 1947.09万</v>
       </c>
       <c r="E7">
@@ -2559,25 +2559,25 @@
       <c r="H7">
         <v>2.35</v>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="66">
         <v>7.48</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="72">
         <v>0.53</v>
       </c>
       <c r="K7" s="74">
         <v>5.64</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="73">
         <v>9.11</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="67">
         <v>3.83</v>
       </c>
-      <c r="N7" s="78">
+      <c r="N7" s="68">
         <v>0.26</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="75">
         <v>-1.45</v>
       </c>
       <c r="P7" s="76">
@@ -2586,14 +2586,14 @@
       <c r="Q7" s="69">
         <v>2.93</v>
       </c>
-      <c r="R7" s="72">
+      <c r="R7" s="77">
         <v>5.28</v>
       </c>
-      <c r="S7" s="77">
+      <c r="S7" s="70">
         <v>3.55</v>
       </c>
-      <c r="T7" s="66">
-        <v>-4.34</v>
+      <c r="T7" s="71">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="8">
@@ -2606,7 +2606,7 @@
       <c r="C8" t="str">
         <v>603608</v>
       </c>
-      <c r="D8" s="80" t="str">
+      <c r="D8" s="88" t="str">
         <v>净买: 1843.41万</v>
       </c>
       <c r="E8">
@@ -2621,41 +2621,41 @@
       <c r="H8">
         <v>0.09</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="85">
         <v>9.95</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="89">
         <v>9.12</v>
       </c>
-      <c r="K8" s="88">
+      <c r="K8" s="84">
         <v>6.39</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="86">
         <v>3.1</v>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="90">
         <v>1.73</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="91">
         <v>0.27</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8" s="80">
         <v>-0.73</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="87">
         <v>-4.93</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="81">
         <v>-2.46</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="82">
         <v>-5.47</v>
       </c>
-      <c r="S8" s="87">
+      <c r="S8" s="79">
         <v>-5.47</v>
       </c>
-      <c r="T8" s="79">
-        <v>16.51</v>
+      <c r="T8" s="83">
+        <v>18.8</v>
       </c>
     </row>
     <row r="9">
@@ -2717,41 +2717,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="98">
+      <c r="I10" s="93">
         <v>57.14</v>
       </c>
-      <c r="J10" s="94">
+      <c r="J10" s="100">
         <v>71.43</v>
       </c>
-      <c r="K10" s="103">
+      <c r="K10" s="101">
         <v>85.71</v>
       </c>
-      <c r="L10" s="99">
+      <c r="L10" s="102">
         <v>71.43</v>
       </c>
-      <c r="M10" s="97">
+      <c r="M10" s="94">
         <v>71.43</v>
       </c>
-      <c r="N10" s="100">
+      <c r="N10" s="95">
         <v>71.43</v>
       </c>
-      <c r="O10" s="101">
+      <c r="O10" s="96">
         <v>57.14</v>
       </c>
-      <c r="P10" s="92">
+      <c r="P10" s="97">
         <v>57.14</v>
       </c>
-      <c r="Q10" s="95">
+      <c r="Q10" s="98">
         <v>57.14</v>
       </c>
-      <c r="R10" s="96">
+      <c r="R10" s="99">
         <v>71.43</v>
       </c>
-      <c r="S10" s="102">
+      <c r="S10" s="103">
         <v>71.43</v>
       </c>
-      <c r="T10" s="93">
-        <v>28.57</v>
+      <c r="T10" s="92">
+        <v>42.86</v>
       </c>
     </row>
     <row r="11">
@@ -2765,41 +2765,41 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="110">
+      <c r="I11" s="112">
         <v>3.71</v>
       </c>
-      <c r="J11" s="105">
+      <c r="J11" s="113">
         <v>6.5</v>
       </c>
       <c r="K11" s="106">
         <v>7.96</v>
       </c>
-      <c r="L11" s="111">
+      <c r="L11" s="107">
         <v>6.53</v>
       </c>
-      <c r="M11" s="112">
+      <c r="M11" s="108">
         <v>1.01</v>
       </c>
-      <c r="N11" s="113">
+      <c r="N11" s="110">
         <v>-0.51</v>
       </c>
-      <c r="O11" s="114">
+      <c r="O11" s="109">
         <v>0.09</v>
       </c>
-      <c r="P11" s="115">
+      <c r="P11" s="114">
         <v>2.38</v>
       </c>
-      <c r="Q11" s="107">
+      <c r="Q11" s="104">
         <v>3.95</v>
       </c>
-      <c r="R11" s="108">
+      <c r="R11" s="111">
         <v>4.39</v>
       </c>
-      <c r="S11" s="104">
+      <c r="S11" s="115">
         <v>4.03</v>
       </c>
-      <c r="T11" s="109">
-        <v>-6.93</v>
+      <c r="T11" s="105">
+        <v>-4.5</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/交易者单骑/index.xlsx
+++ b/youzi/交易者单骑/index.xlsx
@@ -39,19 +39,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE4E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF9DFE1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,49 +171,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE4E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,55 +363,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,97 +477,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB5"/>
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,67 +543,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF2E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -357,319 +711,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF2E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -682,48 +724,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFED98A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2234,7 +2234,7 @@
       <c r="C2" t="str">
         <v>600192</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="2" t="str">
         <v>净买: 618.00万</v>
       </c>
       <c r="E2">
@@ -2249,13 +2249,13 @@
       <c r="H2">
         <v>5.03</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>4.79</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="4">
         <v>15.28</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="3">
         <v>12.18</v>
       </c>
       <c r="L2" s="5">
@@ -2264,26 +2264,26 @@
       <c r="M2" s="6">
         <v>8.42</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="8">
         <v>2.46</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="13">
         <v>0.78</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="9">
         <v>-1.42</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="7">
         <v>-0.52</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="10">
         <v>1.17</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="11">
         <v>0.65</v>
       </c>
-      <c r="T2" s="10">
-        <v>6.74</v>
+      <c r="T2" s="1">
+        <v>5.18</v>
       </c>
     </row>
     <row r="3">
@@ -2296,7 +2296,7 @@
       <c r="C3" t="str">
         <v>600715</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="21" t="str">
         <v>净买: 1669.10万</v>
       </c>
       <c r="E3">
@@ -2311,41 +2311,41 @@
       <c r="H3">
         <v>0.38</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="17">
         <v>9.74</v>
       </c>
       <c r="J3" s="18">
         <v>10.11</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="22">
         <v>20.97</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="23">
         <v>8.99</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="14">
         <v>0.75</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="24">
         <v>1.12</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="25">
         <v>11.24</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="19">
         <v>13.48</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="20">
         <v>13.11</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="15">
         <v>16.85</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="26">
         <v>14.98</v>
       </c>
-      <c r="T3" s="14">
-        <v>-23.22</v>
+      <c r="T3" s="16">
+        <v>-24.72</v>
       </c>
     </row>
     <row r="4">
@@ -2373,41 +2373,41 @@
       <c r="H4">
         <v>6.44</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="34">
         <v>-2.7</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="37">
         <v>16.76</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="38">
         <v>16.15</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="39">
         <v>10.53</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="30">
         <v>9.95</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="35">
         <v>5.4</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="33">
         <v>1.32</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="31">
         <v>21.58</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="36">
         <v>23.43</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="27">
         <v>21.71</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="32">
         <v>17.16</v>
       </c>
       <c r="T4" s="28">
-        <v>-5.53</v>
+        <v>-8.04</v>
       </c>
     </row>
     <row r="5">
@@ -2420,7 +2420,7 @@
       <c r="C5" t="str">
         <v>000952</v>
       </c>
-      <c r="D5" s="44" t="str">
+      <c r="D5" s="46" t="str">
         <v>净卖: -615.36万</v>
       </c>
       <c r="E5">
@@ -2435,41 +2435,41 @@
       <c r="H5">
         <v>-8.25</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="49">
         <v>-1.97</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="42">
         <v>-5.48</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="52">
         <v>-5.76</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="50">
         <v>-5.06</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="43">
         <v>-6.32</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="44">
         <v>-2.53</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="45">
         <v>1.4</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="47">
         <v>1.83</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="40">
         <v>3.09</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="51">
         <v>3.23</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="41">
         <v>4.63</v>
       </c>
-      <c r="T5" s="50">
-        <v>3.23</v>
+      <c r="T5" s="48">
+        <v>3.65</v>
       </c>
     </row>
     <row r="6">
@@ -2482,7 +2482,7 @@
       <c r="C6" t="str">
         <v>603378</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="64" t="str">
         <v>净卖: -283.77万</v>
       </c>
       <c r="E6">
@@ -2497,41 +2497,41 @@
       <c r="H6">
         <v>-8.77</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="65">
         <v>-1.34</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="57">
         <v>-0.85</v>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="58">
         <v>0.12</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="53">
         <v>-1.46</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="59">
         <v>-11.31</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="62">
         <v>-10.58</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="60">
         <v>-11.92</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="54">
         <v>-14.6</v>
       </c>
       <c r="Q6" s="61">
         <v>-11.92</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="55">
         <v>-12.04</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="63">
         <v>-7.3</v>
       </c>
-      <c r="T6" s="63">
-        <v>-30.29</v>
+      <c r="T6" s="56">
+        <v>-29.56</v>
       </c>
     </row>
     <row r="7">
@@ -2544,7 +2544,7 @@
       <c r="C7" t="str">
         <v>001317</v>
       </c>
-      <c r="D7" s="78" t="str">
+      <c r="D7" s="73" t="str">
         <v>净买: 1947.09万</v>
       </c>
       <c r="E7">
@@ -2559,41 +2559,41 @@
       <c r="H7">
         <v>2.35</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="74">
         <v>7.48</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="75">
         <v>0.53</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="68">
         <v>5.64</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="69">
         <v>9.11</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="70">
         <v>3.83</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="66">
         <v>0.26</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="77">
         <v>-1.45</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="71">
         <v>0.73</v>
       </c>
-      <c r="Q7" s="69">
+      <c r="Q7" s="67">
         <v>2.93</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="78">
         <v>5.28</v>
       </c>
-      <c r="S7" s="70">
+      <c r="S7" s="72">
         <v>3.55</v>
       </c>
-      <c r="T7" s="71">
-        <v>-1.2</v>
+      <c r="T7" s="76">
+        <v>-2.95</v>
       </c>
     </row>
     <row r="8">
@@ -2606,7 +2606,7 @@
       <c r="C8" t="str">
         <v>603608</v>
       </c>
-      <c r="D8" s="88" t="str">
+      <c r="D8" s="86" t="str">
         <v>净买: 1843.41万</v>
       </c>
       <c r="E8">
@@ -2621,41 +2621,41 @@
       <c r="H8">
         <v>0.09</v>
       </c>
-      <c r="I8" s="85">
+      <c r="I8" s="80">
         <v>9.95</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="90">
         <v>9.12</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="87">
         <v>6.39</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="91">
         <v>3.1</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="79">
         <v>1.73</v>
       </c>
-      <c r="N8" s="91">
+      <c r="N8" s="81">
         <v>0.27</v>
       </c>
-      <c r="O8" s="80">
+      <c r="O8" s="88">
         <v>-0.73</v>
       </c>
-      <c r="P8" s="87">
+      <c r="P8" s="82">
         <v>-4.93</v>
       </c>
-      <c r="Q8" s="81">
+      <c r="Q8" s="83">
         <v>-2.46</v>
       </c>
-      <c r="R8" s="82">
+      <c r="R8" s="85">
         <v>-5.47</v>
       </c>
-      <c r="S8" s="79">
+      <c r="S8" s="84">
         <v>-5.47</v>
       </c>
-      <c r="T8" s="83">
-        <v>18.8</v>
+      <c r="T8" s="89">
+        <v>18.98</v>
       </c>
     </row>
     <row r="9">
@@ -2720,37 +2720,37 @@
       <c r="I10" s="93">
         <v>57.14</v>
       </c>
-      <c r="J10" s="100">
+      <c r="J10" s="99">
         <v>71.43</v>
       </c>
-      <c r="K10" s="101">
+      <c r="K10" s="94">
         <v>85.71</v>
       </c>
-      <c r="L10" s="102">
+      <c r="L10" s="101">
         <v>71.43</v>
       </c>
-      <c r="M10" s="94">
+      <c r="M10" s="95">
         <v>71.43</v>
       </c>
-      <c r="N10" s="95">
+      <c r="N10" s="96">
         <v>71.43</v>
       </c>
-      <c r="O10" s="96">
+      <c r="O10" s="102">
         <v>57.14</v>
       </c>
       <c r="P10" s="97">
         <v>57.14</v>
       </c>
-      <c r="Q10" s="98">
+      <c r="Q10" s="103">
         <v>57.14</v>
       </c>
-      <c r="R10" s="99">
+      <c r="R10" s="98">
         <v>71.43</v>
       </c>
-      <c r="S10" s="103">
+      <c r="S10" s="92">
         <v>71.43</v>
       </c>
-      <c r="T10" s="92">
+      <c r="T10" s="100">
         <v>42.86</v>
       </c>
     </row>
@@ -2765,41 +2765,41 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="112">
+      <c r="I11" s="113">
         <v>3.71</v>
       </c>
-      <c r="J11" s="113">
+      <c r="J11" s="108">
         <v>6.5</v>
       </c>
-      <c r="K11" s="106">
+      <c r="K11" s="109">
         <v>7.96</v>
       </c>
-      <c r="L11" s="107">
+      <c r="L11" s="114">
         <v>6.53</v>
       </c>
-      <c r="M11" s="108">
+      <c r="M11" s="115">
         <v>1.01</v>
       </c>
-      <c r="N11" s="110">
+      <c r="N11" s="106">
         <v>-0.51</v>
       </c>
-      <c r="O11" s="109">
+      <c r="O11" s="111">
         <v>0.09</v>
       </c>
-      <c r="P11" s="114">
+      <c r="P11" s="110">
         <v>2.38</v>
       </c>
-      <c r="Q11" s="104">
+      <c r="Q11" s="107">
         <v>3.95</v>
       </c>
-      <c r="R11" s="111">
+      <c r="R11" s="104">
         <v>4.39</v>
       </c>
-      <c r="S11" s="115">
+      <c r="S11" s="105">
         <v>4.03</v>
       </c>
-      <c r="T11" s="105">
-        <v>-4.5</v>
+      <c r="T11" s="112">
+        <v>-5.35</v>
       </c>
     </row>
   </sheetData>
